--- a/database/event/7438/event_7438_evp_summary.xlsx
+++ b/database/event/7438/event_7438_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>10.1435</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>6.2965</v>
       </c>
       <c r="D2" t="n">
         <v>3.6764</v>
@@ -545,7 +545,7 @@
         <v>9.7121</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>6.0287</v>
       </c>
       <c r="D3" t="n">
         <v>3.5021</v>
@@ -591,7 +591,7 @@
         <v>5.8935</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.6583</v>
       </c>
       <c r="D4" t="n">
         <v>1.9595</v>
@@ -637,7 +637,7 @@
         <v>4.4246</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.7465</v>
       </c>
       <c r="D5" t="n">
         <v>1.3661</v>
@@ -683,7 +683,7 @@
         <v>4.3364</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.6918</v>
       </c>
       <c r="D6" t="n">
         <v>1.3304</v>
@@ -729,7 +729,7 @@
         <v>4.318</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.6803</v>
       </c>
       <c r="D7" t="n">
         <v>1.323</v>
@@ -775,7 +775,7 @@
         <v>4.228</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.6245</v>
       </c>
       <c r="D8" t="n">
         <v>1.2867</v>
@@ -821,7 +821,7 @@
         <v>4.0006</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.4833</v>
       </c>
       <c r="D9" t="n">
         <v>1.1948</v>
@@ -867,7 +867,7 @@
         <v>3.8901</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.4147</v>
       </c>
       <c r="D10" t="n">
         <v>1.1502</v>
@@ -913,7 +913,7 @@
         <v>3.7371</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.3198</v>
       </c>
       <c r="D11" t="n">
         <v>1.0883</v>
@@ -959,7 +959,7 @@
         <v>3.6813</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2.2851</v>
       </c>
       <c r="D12" t="n">
         <v>1.0658</v>
@@ -1005,7 +1005,7 @@
         <v>3.4363</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2.133</v>
       </c>
       <c r="D13" t="n">
         <v>0.9668</v>
@@ -1051,7 +1051,7 @@
         <v>3.3926</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2.1059</v>
       </c>
       <c r="D14" t="n">
         <v>0.9492</v>
@@ -1097,7 +1097,7 @@
         <v>3.3257</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2.0644</v>
       </c>
       <c r="D15" t="n">
         <v>0.9221</v>
@@ -1143,7 +1143,7 @@
         <v>3.0692</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.9052</v>
       </c>
       <c r="D16" t="n">
         <v>0.8185</v>
@@ -1189,7 +1189,7 @@
         <v>2.8151</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.7474</v>
       </c>
       <c r="D17" t="n">
         <v>0.7159</v>
@@ -1235,7 +1235,7 @@
         <v>2.6928</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.6715</v>
       </c>
       <c r="D18" t="n">
         <v>0.6665</v>
@@ -1281,7 +1281,7 @@
         <v>2.5994</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.6135</v>
       </c>
       <c r="D19" t="n">
         <v>0.6287</v>
@@ -1327,7 +1327,7 @@
         <v>2.5671</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.5935</v>
       </c>
       <c r="D20" t="n">
         <v>0.6157</v>
@@ -1373,7 +1373,7 @@
         <v>2.2015</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.3666</v>
       </c>
       <c r="D21" t="n">
         <v>0.468</v>
@@ -1419,7 +1419,7 @@
         <v>2.1764</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.351</v>
       </c>
       <c r="D22" t="n">
         <v>0.4579</v>
@@ -1465,7 +1465,7 @@
         <v>2.1322</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.3235</v>
       </c>
       <c r="D23" t="n">
         <v>0.44</v>
@@ -1511,7 +1511,7 @@
         <v>1.9061</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.1832</v>
       </c>
       <c r="D24" t="n">
         <v>0.3487</v>
@@ -1557,7 +1557,7 @@
         <v>1.7342</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.0765</v>
       </c>
       <c r="D25" t="n">
         <v>0.2792</v>
@@ -1603,7 +1603,7 @@
         <v>1.721</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.0683</v>
       </c>
       <c r="D26" t="n">
         <v>0.2739</v>
@@ -1649,7 +1649,7 @@
         <v>1.6749</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.0397</v>
       </c>
       <c r="D27" t="n">
         <v>0.2553</v>
@@ -1695,7 +1695,7 @@
         <v>1.6564</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.0282</v>
       </c>
       <c r="D28" t="n">
         <v>0.2478</v>
@@ -1741,7 +1741,7 @@
         <v>1.6359</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1.0155</v>
       </c>
       <c r="D29" t="n">
         <v>0.2395</v>
@@ -1787,7 +1787,7 @@
         <v>1.6041</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.9957</v>
       </c>
       <c r="D30" t="n">
         <v>0.2267</v>
@@ -1833,7 +1833,7 @@
         <v>1.4529</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.9019</v>
       </c>
       <c r="D31" t="n">
         <v>0.1656</v>
@@ -1879,7 +1879,7 @@
         <v>1.2575</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.7806</v>
       </c>
       <c r="D32" t="n">
         <v>0.0866</v>
@@ -1925,7 +1925,7 @@
         <v>1.2066</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.749</v>
       </c>
       <c r="D33" t="n">
         <v>0.06610000000000001</v>
@@ -1971,7 +1971,7 @@
         <v>1.0767</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.6683</v>
       </c>
       <c r="D34" t="n">
         <v>0.0136</v>
@@ -2017,7 +2017,7 @@
         <v>1.0644</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.6607</v>
       </c>
       <c r="D35" t="n">
         <v>0.0086</v>
@@ -2063,7 +2063,7 @@
         <v>1.0597</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="D36" t="n">
         <v>0.0067</v>
@@ -2109,7 +2109,7 @@
         <v>0.9664</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.5999</v>
       </c>
       <c r="D37" t="n">
         <v>-0.031</v>
@@ -2155,7 +2155,7 @@
         <v>0.78</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.4842</v>
       </c>
       <c r="D38" t="n">
         <v>-0.1063</v>
@@ -2201,7 +2201,7 @@
         <v>0.6798999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.422</v>
       </c>
       <c r="D39" t="n">
         <v>-0.1467</v>
@@ -2247,7 +2247,7 @@
         <v>0.6677</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.4145</v>
       </c>
       <c r="D40" t="n">
         <v>-0.1516</v>
@@ -2293,7 +2293,7 @@
         <v>0.5591</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.3471</v>
       </c>
       <c r="D41" t="n">
         <v>-0.1955</v>
@@ -2339,7 +2339,7 @@
         <v>0.3869</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="D42" t="n">
         <v>-0.2651</v>
@@ -2385,7 +2385,7 @@
         <v>0.3448</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="D43" t="n">
         <v>-0.2821</v>
@@ -2431,7 +2431,7 @@
         <v>0.272</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.1688</v>
       </c>
       <c r="D44" t="n">
         <v>-0.3115</v>
@@ -2477,7 +2477,7 @@
         <v>0.2561</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.159</v>
       </c>
       <c r="D45" t="n">
         <v>-0.3179</v>
@@ -2523,7 +2523,7 @@
         <v>0.2544</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.1579</v>
       </c>
       <c r="D46" t="n">
         <v>-0.3186</v>
@@ -2569,7 +2569,7 @@
         <v>0.2255</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="D47" t="n">
         <v>-0.3303</v>
@@ -2615,7 +2615,7 @@
         <v>0.2063</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.1281</v>
       </c>
       <c r="D48" t="n">
         <v>-0.338</v>
@@ -2661,7 +2661,7 @@
         <v>0.0563</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.0349</v>
       </c>
       <c r="D49" t="n">
         <v>-0.3986</v>
@@ -2707,7 +2707,7 @@
         <v>0.0529</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.0328</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4</v>
@@ -2753,7 +2753,7 @@
         <v>-0.0198</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.0123</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4294</v>
@@ -2799,7 +2799,7 @@
         <v>-0.1351</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.0839</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4759</v>
@@ -2845,7 +2845,7 @@
         <v>-0.1514</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.094</v>
       </c>
       <c r="D53" t="n">
         <v>-0.4825</v>
@@ -2891,7 +2891,7 @@
         <v>-0.1653</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.1026</v>
       </c>
       <c r="D54" t="n">
         <v>-0.4881</v>
@@ -2937,7 +2937,7 @@
         <v>-0.1723</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.107</v>
       </c>
       <c r="D55" t="n">
         <v>-0.491</v>
@@ -2983,7 +2983,7 @@
         <v>-0.2381</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.1478</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5175</v>
@@ -3029,7 +3029,7 @@
         <v>-0.3512</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.218</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5632</v>
@@ -3075,7 +3075,7 @@
         <v>-0.3865</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.2399</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5775</v>
@@ -3121,7 +3121,7 @@
         <v>-0.4695</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2914</v>
       </c>
       <c r="D59" t="n">
         <v>-0.611</v>
@@ -3167,7 +3167,7 @@
         <v>-0.5524</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.3429</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6445</v>
@@ -3213,7 +3213,7 @@
         <v>-0.5971</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.3706</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6626</v>
@@ -3259,7 +3259,7 @@
         <v>-0.6163</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.3826</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6703</v>
@@ -3305,7 +3305,7 @@
         <v>-0.6467000000000001</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.4014</v>
       </c>
       <c r="D63" t="n">
         <v>-0.6826</v>
@@ -3351,7 +3351,7 @@
         <v>-0.7358</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.4567</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7186</v>
@@ -3397,7 +3397,7 @@
         <v>-0.8759</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.5437</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7752</v>
@@ -3443,7 +3443,7 @@
         <v>-0.9364</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.5813</v>
       </c>
       <c r="D66" t="n">
         <v>-0.7996</v>
@@ -3489,7 +3489,7 @@
         <v>-0.9553</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.593</v>
       </c>
       <c r="D67" t="n">
         <v>-0.8073</v>
@@ -3535,7 +3535,7 @@
         <v>-1.0075</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.6254</v>
       </c>
       <c r="D68" t="n">
         <v>-0.8284</v>
@@ -3581,7 +3581,7 @@
         <v>-1.1559</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.7175</v>
       </c>
       <c r="D69" t="n">
         <v>-0.8883</v>
@@ -3627,7 +3627,7 @@
         <v>-1.2339</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.7659</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9198</v>
@@ -3673,7 +3673,7 @@
         <v>-1.3178</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="D71" t="n">
         <v>-0.9537</v>
@@ -3719,7 +3719,7 @@
         <v>-1.3955</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.8662</v>
       </c>
       <c r="D72" t="n">
         <v>-0.9851</v>
@@ -3765,7 +3765,7 @@
         <v>-1.5336</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.952</v>
       </c>
       <c r="D73" t="n">
         <v>-1.0409</v>
@@ -3811,7 +3811,7 @@
         <v>-1.5665</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.9724</v>
       </c>
       <c r="D74" t="n">
         <v>-1.0542</v>
@@ -3857,7 +3857,7 @@
         <v>-1.5796</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.9805</v>
       </c>
       <c r="D75" t="n">
         <v>-1.0595</v>
@@ -3903,7 +3903,7 @@
         <v>-1.7372</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.0783</v>
       </c>
       <c r="D76" t="n">
         <v>-1.1232</v>
@@ -3949,7 +3949,7 @@
         <v>-1.8947</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.1761</v>
       </c>
       <c r="D77" t="n">
         <v>-1.1868</v>
@@ -3995,7 +3995,7 @@
         <v>-2.0682</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.2838</v>
       </c>
       <c r="D78" t="n">
         <v>-1.2569</v>
@@ -4041,7 +4041,7 @@
         <v>-3.4576</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-2.1463</v>
       </c>
       <c r="D79" t="n">
         <v>-1.8182</v>
@@ -4087,7 +4087,7 @@
         <v>-3.8082</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-2.3639</v>
       </c>
       <c r="D80" t="n">
         <v>-1.9598</v>
@@ -4133,7 +4133,7 @@
         <v>-4.9826</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-3.0929</v>
       </c>
       <c r="D81" t="n">
         <v>-2.4342</v>

--- a/database/event/7438/event_7438_evp_summary.xlsx
+++ b/database/event/7438/event_7438_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.1435</v>
+        <v>10.9131</v>
       </c>
       <c r="C2" t="n">
-        <v>6.2965</v>
+        <v>6.7742</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6764</v>
+        <v>3.9039</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1435</v>
+        <v>10.9131</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4957</v>
+        <v>4.2653</v>
       </c>
       <c r="G2" t="n">
         <v>6.6478</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4957</v>
+        <v>4.385</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5283</v>
+        <v>4.4591</v>
       </c>
       <c r="J2" t="n">
         <v>8.126799999999999</v>
@@ -529,7 +529,7 @@
         <v>166</v>
       </c>
       <c r="M2" t="n">
-        <v>11.6551</v>
+        <v>12.5859</v>
       </c>
       <c r="N2" t="n">
         <v>357</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.7121</v>
+        <v>9.6883</v>
       </c>
       <c r="C3" t="n">
-        <v>6.0287</v>
+        <v>6.0139</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5021</v>
+        <v>3.4159</v>
       </c>
       <c r="E3" t="n">
-        <v>9.7121</v>
+        <v>9.6883</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2036</v>
+        <v>3.1798</v>
       </c>
       <c r="G3" t="n">
         <v>6.5085</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2036</v>
+        <v>3.1798</v>
       </c>
       <c r="I3" t="n">
         <v>3.2335</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8935</v>
+        <v>6.5972</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6583</v>
+        <v>4.0951</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9595</v>
+        <v>2.1844</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8935</v>
+        <v>6.5972</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9556</v>
+        <v>2.6593</v>
       </c>
       <c r="G4" t="n">
         <v>3.9379</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9556</v>
+        <v>2.6593</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9556</v>
+        <v>2.6593</v>
       </c>
       <c r="J4" t="n">
         <v>3.9379</v>
@@ -621,7 +621,7 @@
         <v>164</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8935</v>
+        <v>6.5972</v>
       </c>
       <c r="N4" t="n">
         <v>281</v>
@@ -630,127 +630,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4246</v>
+        <v>4.6929</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7465</v>
+        <v>2.9131</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3661</v>
+        <v>1.4257</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4246</v>
+        <v>4.6929</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4354</v>
+        <v>3.9878</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9892</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4354</v>
+        <v>3.9878</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4354</v>
+        <v>3.2322</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9892</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="L5" t="n">
-        <v>164</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4246</v>
+        <v>3.9373</v>
       </c>
       <c r="N5" t="n">
-        <v>281</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3364</v>
+        <v>4.4246</v>
       </c>
       <c r="C6" t="n">
-        <v>2.6918</v>
+        <v>2.7465</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3304</v>
+        <v>1.3189</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3364</v>
+        <v>4.4246</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3935</v>
+        <v>2.4354</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0571</v>
+        <v>1.9892</v>
       </c>
       <c r="H6" t="n">
-        <v>5.1156</v>
+        <v>2.4354</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1463</v>
+        <v>2.4354</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0571</v>
+        <v>1.9892</v>
       </c>
       <c r="K6" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="L6" t="n">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="M6" t="n">
-        <v>4.0892</v>
+        <v>4.4246</v>
       </c>
       <c r="N6" t="n">
-        <v>142</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.318</v>
+        <v>4.3913</v>
       </c>
       <c r="C7" t="n">
-        <v>2.6803</v>
+        <v>2.7258</v>
       </c>
       <c r="D7" t="n">
-        <v>1.323</v>
+        <v>1.3056</v>
       </c>
       <c r="E7" t="n">
-        <v>4.318</v>
+        <v>4.3913</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6129</v>
+        <v>4.4484</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7050999999999999</v>
+        <v>-0.0571</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6129</v>
+        <v>5.3363</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9283</v>
+        <v>4.3252</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7050999999999999</v>
+        <v>-0.0571</v>
       </c>
       <c r="K7" t="n">
         <v>99</v>
@@ -759,7 +759,7 @@
         <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6334</v>
+        <v>4.2681</v>
       </c>
       <c r="N7" t="n">
         <v>142</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.228</v>
+        <v>4.3349</v>
       </c>
       <c r="C8" t="n">
-        <v>2.6245</v>
+        <v>2.6908</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2867</v>
+        <v>1.2831</v>
       </c>
       <c r="E8" t="n">
-        <v>4.228</v>
+        <v>4.3349</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0542</v>
+        <v>4.3349</v>
       </c>
       <c r="G8" t="n">
-        <v>4.1738</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0542</v>
+        <v>4.494</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0542</v>
+        <v>4.57</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1738</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>117</v>
+        <v>229</v>
       </c>
       <c r="L8" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.228</v>
+        <v>4.57</v>
       </c>
       <c r="N8" t="n">
-        <v>281</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.0006</v>
+        <v>4.228</v>
       </c>
       <c r="C9" t="n">
-        <v>2.4833</v>
+        <v>2.6245</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1948</v>
+        <v>1.2405</v>
       </c>
       <c r="E9" t="n">
-        <v>4.0006</v>
+        <v>4.228</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1568</v>
+        <v>0.0542</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1562</v>
+        <v>4.1738</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1633</v>
+        <v>0.0542</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3744</v>
+        <v>0.0542</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1562</v>
+        <v>4.1738</v>
       </c>
       <c r="K9" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2182</v>
+        <v>4.228</v>
       </c>
       <c r="N9" t="n">
-        <v>142</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.8901</v>
+        <v>4.1369</v>
       </c>
       <c r="C10" t="n">
-        <v>2.4147</v>
+        <v>2.5679</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1502</v>
+        <v>1.2042</v>
       </c>
       <c r="E10" t="n">
-        <v>3.8901</v>
+        <v>4.1369</v>
       </c>
       <c r="F10" t="n">
-        <v>3.8901</v>
+        <v>4.2931</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.1562</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8901</v>
+        <v>4.7115</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9264</v>
+        <v>3.8188</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.1562</v>
       </c>
       <c r="K10" t="n">
-        <v>229</v>
+        <v>99</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9264</v>
+        <v>3.6626</v>
       </c>
       <c r="N10" t="n">
-        <v>229</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.7371</v>
+        <v>3.7408</v>
       </c>
       <c r="C11" t="n">
-        <v>2.3198</v>
+        <v>2.3221</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0883</v>
+        <v>1.0464</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7371</v>
+        <v>3.7408</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4897</v>
+        <v>-0.4861</v>
       </c>
       <c r="G11" t="n">
         <v>4.2268</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4897</v>
+        <v>-0.4861</v>
       </c>
       <c r="I11" t="n">
         <v>-0.4943</v>
@@ -962,7 +962,7 @@
         <v>2.2851</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0658</v>
+        <v>1.0227</v>
       </c>
       <c r="E12" t="n">
         <v>3.6813</v>
@@ -1008,7 +1008,7 @@
         <v>2.133</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9668</v>
+        <v>0.9251</v>
       </c>
       <c r="E13" t="n">
         <v>3.4363</v>
@@ -1054,7 +1054,7 @@
         <v>2.1059</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9492</v>
+        <v>0.9077</v>
       </c>
       <c r="E14" t="n">
         <v>3.3926</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.3257</v>
+        <v>3.2943</v>
       </c>
       <c r="C15" t="n">
-        <v>2.0644</v>
+        <v>2.0449</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9221</v>
+        <v>0.8685</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3257</v>
+        <v>3.2943</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2831</v>
+        <v>4.2517</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9574</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4128</v>
+        <v>4.3636</v>
       </c>
       <c r="I15" t="n">
         <v>4.4747</v>
@@ -1146,7 +1146,7 @@
         <v>1.9052</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8185</v>
+        <v>0.7789</v>
       </c>
       <c r="E16" t="n">
         <v>3.0692</v>
@@ -1182,124 +1182,124 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8151</v>
+        <v>2.8753</v>
       </c>
       <c r="C17" t="n">
-        <v>1.7474</v>
+        <v>1.7848</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7159</v>
+        <v>0.7016</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8151</v>
+        <v>2.8753</v>
       </c>
       <c r="F17" t="n">
-        <v>3.8151</v>
+        <v>2.8753</v>
       </c>
       <c r="G17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8151</v>
+        <v>2.8753</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8687</v>
+        <v>2.8995</v>
       </c>
       <c r="J17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="L17" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8687</v>
+        <v>2.8995</v>
       </c>
       <c r="N17" t="n">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6928</v>
+        <v>2.7726</v>
       </c>
       <c r="C18" t="n">
-        <v>1.6715</v>
+        <v>1.7211</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6665</v>
+        <v>0.6607</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6928</v>
+        <v>2.7726</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6928</v>
+        <v>3.7726</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6928</v>
+        <v>3.7726</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7053</v>
+        <v>3.8687</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K18" t="n">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7053</v>
+        <v>2.8687</v>
       </c>
       <c r="N18" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.5994</v>
+        <v>2.6828</v>
       </c>
       <c r="C19" t="n">
-        <v>1.6135</v>
+        <v>1.6653</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6287</v>
+        <v>0.6249</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5994</v>
+        <v>2.6828</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5994</v>
+        <v>2.6828</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5994</v>
+        <v>2.6828</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6115</v>
+        <v>2.7053</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.6115</v>
+        <v>2.7053</v>
       </c>
       <c r="N19" t="n">
         <v>167</v>
@@ -1330,7 +1330,7 @@
         <v>1.5935</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6157</v>
+        <v>0.5788</v>
       </c>
       <c r="E20" t="n">
         <v>2.5671</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.2015</v>
+        <v>2.4732</v>
       </c>
       <c r="C21" t="n">
-        <v>1.3666</v>
+        <v>1.5352</v>
       </c>
       <c r="D21" t="n">
-        <v>0.468</v>
+        <v>0.5414</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2015</v>
+        <v>2.4732</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2015</v>
+        <v>2.4732</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2015</v>
+        <v>2.4732</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2015</v>
+        <v>2.4732</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.2015</v>
+        <v>2.4732</v>
       </c>
       <c r="N21" t="n">
-        <v>129</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.1764</v>
+        <v>2.2958</v>
       </c>
       <c r="C22" t="n">
-        <v>1.351</v>
+        <v>1.4251</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4579</v>
+        <v>0.4707</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1764</v>
+        <v>2.2958</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1764</v>
+        <v>2.2958</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1764</v>
+        <v>2.2958</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1967</v>
+        <v>2.3346</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.1967</v>
+        <v>2.3346</v>
       </c>
       <c r="N22" t="n">
         <v>229</v>
@@ -1458,265 +1458,265 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.1322</v>
+        <v>2.2015</v>
       </c>
       <c r="C23" t="n">
-        <v>1.3235</v>
+        <v>1.3666</v>
       </c>
       <c r="D23" t="n">
-        <v>0.44</v>
+        <v>0.4332</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1322</v>
+        <v>2.2015</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1322</v>
+        <v>2.2015</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.1322</v>
+        <v>2.2015</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1421</v>
+        <v>2.2015</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.1421</v>
+        <v>2.2015</v>
       </c>
       <c r="N23" t="n">
-        <v>167</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HUASOPEEK</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9061</v>
+        <v>2.1242</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1832</v>
+        <v>1.3186</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3487</v>
+        <v>0.4024</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9061</v>
+        <v>2.1242</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5706</v>
+        <v>2.1242</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3355</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5706</v>
+        <v>2.1242</v>
       </c>
       <c r="I24" t="n">
-        <v>1.273</v>
+        <v>2.1421</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3355</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="L24" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.6085</v>
+        <v>2.1421</v>
       </c>
       <c r="N24" t="n">
-        <v>194</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>HUASOPEEK</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7342</v>
+        <v>1.9061</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0765</v>
+        <v>1.1832</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2792</v>
+        <v>0.3155</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7342</v>
+        <v>1.9061</v>
       </c>
       <c r="F25" t="n">
-        <v>2.7342</v>
+        <v>1.5706</v>
       </c>
       <c r="G25" t="n">
-        <v>-1</v>
+        <v>0.3355</v>
       </c>
       <c r="H25" t="n">
-        <v>2.7342</v>
+        <v>1.5706</v>
       </c>
       <c r="I25" t="n">
-        <v>2.7725</v>
+        <v>1.273</v>
       </c>
       <c r="J25" t="n">
-        <v>-1</v>
+        <v>0.3355</v>
       </c>
       <c r="K25" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="L25" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="M25" t="n">
-        <v>1.7725</v>
+        <v>1.6085</v>
       </c>
       <c r="N25" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.721</v>
+        <v>1.7456</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0683</v>
+        <v>1.0836</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2739</v>
+        <v>0.2515</v>
       </c>
       <c r="E26" t="n">
-        <v>1.721</v>
+        <v>1.7456</v>
       </c>
       <c r="F26" t="n">
-        <v>1.721</v>
+        <v>2.3691</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>1.721</v>
+        <v>2.3691</v>
       </c>
       <c r="I26" t="n">
-        <v>1.721</v>
+        <v>2.3691</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>1.721</v>
+        <v>1.7456</v>
       </c>
       <c r="N26" t="n">
-        <v>152</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6749</v>
+        <v>1.7144</v>
       </c>
       <c r="C27" t="n">
-        <v>1.0397</v>
+        <v>1.0642</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2553</v>
+        <v>0.2391</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6749</v>
+        <v>1.7144</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6749</v>
+        <v>1.9756</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.2612</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6749</v>
+        <v>1.9756</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6749</v>
+        <v>1.6013</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.2612</v>
       </c>
       <c r="K27" t="n">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6749</v>
+        <v>1.3401</v>
       </c>
       <c r="N27" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6564</v>
+        <v>1.7037</v>
       </c>
       <c r="C28" t="n">
-        <v>1.0282</v>
+        <v>1.0576</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2478</v>
+        <v>0.2348</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6564</v>
+        <v>1.7037</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0287</v>
+        <v>2.7037</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6277</v>
+        <v>-1</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0287</v>
+        <v>2.7037</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0431</v>
+        <v>2.7725</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6277</v>
+        <v>-1</v>
       </c>
       <c r="K28" t="n">
         <v>140</v>
@@ -1725,7 +1725,7 @@
         <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6708</v>
+        <v>1.7725</v>
       </c>
       <c r="N28" t="n">
         <v>176</v>
@@ -1734,403 +1734,403 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.6359</v>
+        <v>1.6749</v>
       </c>
       <c r="C29" t="n">
-        <v>1.0155</v>
+        <v>1.0397</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2395</v>
+        <v>0.2234</v>
       </c>
       <c r="E29" t="n">
-        <v>1.6359</v>
+        <v>1.6749</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6359</v>
+        <v>1.6749</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6359</v>
+        <v>1.6749</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6359</v>
+        <v>1.6749</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.6359</v>
+        <v>1.6749</v>
       </c>
       <c r="N29" t="n">
-        <v>162</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.6041</v>
+        <v>1.6449</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9957</v>
+        <v>1.0211</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2267</v>
+        <v>0.2114</v>
       </c>
       <c r="E30" t="n">
-        <v>1.6041</v>
+        <v>1.6449</v>
       </c>
       <c r="F30" t="n">
-        <v>1.8653</v>
+        <v>1.0172</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.2612</v>
+        <v>0.6277</v>
       </c>
       <c r="H30" t="n">
-        <v>1.8653</v>
+        <v>1.0172</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5118</v>
+        <v>1.0431</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2612</v>
+        <v>0.6277</v>
       </c>
       <c r="K30" t="n">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="L30" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="M30" t="n">
-        <v>1.2506</v>
+        <v>1.6708</v>
       </c>
       <c r="N30" t="n">
-        <v>142</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.4529</v>
+        <v>1.6359</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9019</v>
+        <v>1.0155</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1656</v>
+        <v>0.2078</v>
       </c>
       <c r="E31" t="n">
-        <v>1.4529</v>
+        <v>1.6359</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4529</v>
+        <v>1.6359</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4529</v>
+        <v>1.6359</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4529</v>
+        <v>1.6359</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>63</v>
+        <v>162</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4529</v>
+        <v>1.6359</v>
       </c>
       <c r="N31" t="n">
-        <v>63</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.2575</v>
+        <v>1.4529</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7806</v>
+        <v>0.9019</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0866</v>
+        <v>0.1349</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2575</v>
+        <v>1.4529</v>
       </c>
       <c r="F32" t="n">
-        <v>1.2575</v>
+        <v>1.4529</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.2575</v>
+        <v>1.4529</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2575</v>
+        <v>1.4529</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2575</v>
+        <v>1.4529</v>
       </c>
       <c r="N32" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.2066</v>
+        <v>1.2575</v>
       </c>
       <c r="C33" t="n">
-        <v>0.749</v>
+        <v>0.7806</v>
       </c>
       <c r="D33" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0571</v>
       </c>
       <c r="E33" t="n">
-        <v>1.2066</v>
+        <v>1.2575</v>
       </c>
       <c r="F33" t="n">
-        <v>1.2066</v>
+        <v>1.2575</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2066</v>
+        <v>1.2575</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2066</v>
+        <v>1.2575</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2066</v>
+        <v>1.2575</v>
       </c>
       <c r="N33" t="n">
-        <v>62</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>prosus</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0767</v>
+        <v>1.2097</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6683</v>
+        <v>0.7509</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0136</v>
+        <v>0.038</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0767</v>
+        <v>1.2097</v>
       </c>
       <c r="F34" t="n">
-        <v>1.0767</v>
+        <v>1.976</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.7663</v>
       </c>
       <c r="H34" t="n">
-        <v>1.0767</v>
+        <v>1.976</v>
       </c>
       <c r="I34" t="n">
-        <v>1.0817</v>
+        <v>1.6016</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.7663</v>
       </c>
       <c r="K34" t="n">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0817</v>
+        <v>0.8352999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>167</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.0644</v>
+        <v>1.2066</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6607</v>
+        <v>0.749</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0086</v>
+        <v>0.0368</v>
       </c>
       <c r="E35" t="n">
-        <v>1.0644</v>
+        <v>1.2066</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0644</v>
+        <v>1.2066</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.0644</v>
+        <v>1.2066</v>
       </c>
       <c r="I35" t="n">
-        <v>1.0644</v>
+        <v>1.2066</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>152</v>
+        <v>62</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.0644</v>
+        <v>1.2066</v>
       </c>
       <c r="N35" t="n">
-        <v>152</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>prosus</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.0597</v>
+        <v>1.0727</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.6659</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0067</v>
+        <v>-0.0165</v>
       </c>
       <c r="E36" t="n">
-        <v>1.0597</v>
+        <v>1.0727</v>
       </c>
       <c r="F36" t="n">
-        <v>1.5162</v>
+        <v>1.0727</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.4565</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.5162</v>
+        <v>1.0727</v>
       </c>
       <c r="I36" t="n">
-        <v>1.5162</v>
+        <v>1.0817</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.4565</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="L36" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.0597</v>
+        <v>1.0817</v>
       </c>
       <c r="N36" t="n">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9664</v>
+        <v>1.0726</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5999</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.031</v>
+        <v>-0.0166</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9664</v>
+        <v>1.0726</v>
       </c>
       <c r="F37" t="n">
-        <v>1.5899</v>
+        <v>1.5291</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.4565</v>
       </c>
       <c r="H37" t="n">
-        <v>1.5899</v>
+        <v>1.5291</v>
       </c>
       <c r="I37" t="n">
-        <v>1.5899</v>
+        <v>1.5291</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.4565</v>
       </c>
       <c r="K37" t="n">
         <v>142</v>
@@ -2139,7 +2139,7 @@
         <v>36</v>
       </c>
       <c r="M37" t="n">
-        <v>0.9664</v>
+        <v>1.0726</v>
       </c>
       <c r="N37" t="n">
         <v>178</v>
@@ -2148,1197 +2148,1197 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.78</v>
+        <v>1.0644</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4842</v>
+        <v>0.6607</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1063</v>
+        <v>-0.0199</v>
       </c>
       <c r="E38" t="n">
-        <v>0.78</v>
+        <v>1.0644</v>
       </c>
       <c r="F38" t="n">
-        <v>1.5031</v>
+        <v>1.0644</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.7231</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.5031</v>
+        <v>1.0644</v>
       </c>
       <c r="I38" t="n">
-        <v>1.5031</v>
+        <v>1.0644</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7231</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="L38" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7800000000000001</v>
+        <v>1.0644</v>
       </c>
       <c r="N38" t="n">
-        <v>178</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.9029</v>
       </c>
       <c r="C39" t="n">
-        <v>0.422</v>
+        <v>0.5605</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1467</v>
+        <v>-0.0842</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.9029</v>
       </c>
       <c r="F39" t="n">
-        <v>1.6799</v>
+        <v>1.626</v>
       </c>
       <c r="G39" t="n">
-        <v>-1</v>
+        <v>-0.7231</v>
       </c>
       <c r="H39" t="n">
-        <v>1.6799</v>
+        <v>1.626</v>
       </c>
       <c r="I39" t="n">
-        <v>1.3616</v>
+        <v>1.626</v>
       </c>
       <c r="J39" t="n">
-        <v>-1</v>
+        <v>-0.7231</v>
       </c>
       <c r="K39" t="n">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="L39" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3615999999999999</v>
+        <v>0.9028999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>max</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6677</v>
+        <v>0.8244</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4145</v>
+        <v>0.5117</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1516</v>
+        <v>-0.1155</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6677</v>
+        <v>0.8244</v>
       </c>
       <c r="F40" t="n">
-        <v>1.434</v>
+        <v>1.8244</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7663</v>
+        <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>1.434</v>
+        <v>1.8244</v>
       </c>
       <c r="I40" t="n">
-        <v>1.1623</v>
+        <v>1.4787</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7663</v>
+        <v>-1</v>
       </c>
       <c r="K40" t="n">
-        <v>99</v>
+        <v>149</v>
       </c>
       <c r="L40" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3960000000000001</v>
+        <v>0.4786999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>142</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5591</v>
+        <v>0.6967</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3471</v>
+        <v>0.4325</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1955</v>
+        <v>-0.1663</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5591</v>
+        <v>0.6967</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5591</v>
+        <v>0.6967</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5591</v>
+        <v>0.6967</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5591</v>
+        <v>0.6967</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5591</v>
+        <v>0.6967</v>
       </c>
       <c r="N41" t="n">
-        <v>162</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hAdji</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3869</v>
+        <v>0.6229</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2402</v>
+        <v>0.3867</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2651</v>
+        <v>-0.1957</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3869</v>
+        <v>0.6229</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3869</v>
+        <v>0.6229</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3869</v>
+        <v>0.6229</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3869</v>
+        <v>0.6229</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>68</v>
+        <v>162</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3869</v>
+        <v>0.6229</v>
       </c>
       <c r="N42" t="n">
-        <v>68</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3448</v>
+        <v>0.5819</v>
       </c>
       <c r="C43" t="n">
-        <v>0.214</v>
+        <v>0.3612</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2821</v>
+        <v>-0.2121</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3448</v>
+        <v>0.5819</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3448</v>
+        <v>0.5819</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3448</v>
+        <v>0.5819</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3448</v>
+        <v>0.5917</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3448</v>
+        <v>0.5917</v>
       </c>
       <c r="N43" t="n">
-        <v>162</v>
+        <v>229</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.272</v>
+        <v>0.5591</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1688</v>
+        <v>0.3471</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3115</v>
+        <v>-0.2212</v>
       </c>
       <c r="E44" t="n">
-        <v>0.272</v>
+        <v>0.5591</v>
       </c>
       <c r="F44" t="n">
-        <v>0.272</v>
+        <v>0.5591</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.272</v>
+        <v>0.5591</v>
       </c>
       <c r="I44" t="n">
-        <v>0.272</v>
+        <v>0.5591</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.272</v>
+        <v>0.5591</v>
       </c>
       <c r="N44" t="n">
-        <v>103</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2561</v>
+        <v>0.4876</v>
       </c>
       <c r="C45" t="n">
-        <v>0.159</v>
+        <v>0.3027</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3179</v>
+        <v>-0.2497</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2561</v>
+        <v>0.4876</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2561</v>
+        <v>0.0281</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.4595</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2561</v>
+        <v>0.0281</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2561</v>
+        <v>0.0281</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.4595</v>
       </c>
       <c r="K45" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2561</v>
+        <v>0.4876</v>
       </c>
       <c r="N45" t="n">
-        <v>103</v>
+        <v>281</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>hAdji</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2544</v>
+        <v>0.3869</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1579</v>
+        <v>0.2402</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3186</v>
+        <v>-0.2898</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2544</v>
+        <v>0.3869</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.2051</v>
+        <v>0.3869</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4595</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.2051</v>
+        <v>0.3869</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2051</v>
+        <v>0.3869</v>
       </c>
       <c r="J46" t="n">
-        <v>0.4595</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="L46" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2544</v>
+        <v>0.3869</v>
       </c>
       <c r="N46" t="n">
-        <v>281</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2255</v>
+        <v>0.2561</v>
       </c>
       <c r="C47" t="n">
-        <v>0.14</v>
+        <v>0.159</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3303</v>
+        <v>-0.3419</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2255</v>
+        <v>0.2561</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2255</v>
+        <v>0.2561</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2255</v>
+        <v>0.2561</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2255</v>
+        <v>0.2561</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2255</v>
+        <v>0.2561</v>
       </c>
       <c r="N47" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.2063</v>
+        <v>0.2255</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1281</v>
+        <v>0.14</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.338</v>
+        <v>-0.3541</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2063</v>
+        <v>0.2255</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2063</v>
+        <v>0.2255</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2063</v>
+        <v>0.2255</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2063</v>
+        <v>0.2255</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.2063</v>
+        <v>0.2255</v>
       </c>
       <c r="N48" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0563</v>
+        <v>0.2063</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0349</v>
+        <v>0.1281</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3986</v>
+        <v>-0.3617</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0563</v>
+        <v>0.2063</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0563</v>
+        <v>0.2063</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0563</v>
+        <v>0.2063</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0563</v>
+        <v>0.2063</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.0563</v>
+        <v>0.2063</v>
       </c>
       <c r="N49" t="n">
-        <v>62</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0529</v>
+        <v>0.1055</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0328</v>
+        <v>0.0655</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4</v>
+        <v>-0.4019</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0529</v>
+        <v>0.1055</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0529</v>
+        <v>0.1055</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0529</v>
+        <v>0.1055</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0534</v>
+        <v>0.1055</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>229</v>
+        <v>152</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0534</v>
+        <v>0.1055</v>
       </c>
       <c r="N50" t="n">
-        <v>229</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>buda</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0198</v>
+        <v>0.0956</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0123</v>
+        <v>0.0593</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4294</v>
+        <v>-0.4058</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0198</v>
+        <v>0.0956</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0198</v>
+        <v>0.569</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.4734</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0198</v>
+        <v>0.569</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0198</v>
+        <v>0.4612</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-0.4734</v>
       </c>
       <c r="K51" t="n">
-        <v>68</v>
+        <v>149</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0198</v>
+        <v>-0.01219999999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>68</v>
+        <v>194</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1351</v>
+        <v>0.0563</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0839</v>
+        <v>0.0349</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4759</v>
+        <v>-0.4215</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1351</v>
+        <v>0.0563</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1351</v>
+        <v>0.0563</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1351</v>
+        <v>0.0563</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1351</v>
+        <v>0.0563</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1351</v>
+        <v>0.0563</v>
       </c>
       <c r="N52" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1514</v>
+        <v>-0.0198</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.094</v>
+        <v>-0.0123</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4825</v>
+        <v>-0.4518</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1514</v>
+        <v>-0.0198</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1514</v>
+        <v>-0.0198</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1514</v>
+        <v>-0.0198</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1514</v>
+        <v>-0.0198</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>152</v>
+        <v>68</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.1514</v>
+        <v>-0.0198</v>
       </c>
       <c r="N53" t="n">
-        <v>152</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1653</v>
+        <v>-0.1351</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1026</v>
+        <v>-0.0839</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4881</v>
+        <v>-0.4977</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1653</v>
+        <v>-0.1351</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1652</v>
+        <v>-0.1351</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.3305</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1652</v>
+        <v>-0.1351</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1652</v>
+        <v>-0.1351</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.3305</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="L54" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.1653</v>
+        <v>-0.1351</v>
       </c>
       <c r="N54" t="n">
-        <v>178</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1723</v>
+        <v>-0.1514</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.107</v>
+        <v>-0.094</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.491</v>
+        <v>-0.5042</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1723</v>
+        <v>-0.1514</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1723</v>
+        <v>-0.1514</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.1723</v>
+        <v>-0.1514</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1723</v>
+        <v>-0.1514</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.1723</v>
+        <v>-0.1514</v>
       </c>
       <c r="N55" t="n">
-        <v>97</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2381</v>
+        <v>-0.1653</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1478</v>
+        <v>-0.1026</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5175</v>
+        <v>-0.5098</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2381</v>
+        <v>-0.1653</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2381</v>
+        <v>0.1652</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>-0.3305</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2381</v>
+        <v>0.1652</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2381</v>
+        <v>0.1652</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>-0.3305</v>
       </c>
       <c r="K56" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2381</v>
+        <v>-0.1653</v>
       </c>
       <c r="N56" t="n">
-        <v>129</v>
+        <v>178</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kRaSnaL</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3512</v>
+        <v>-0.1723</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.218</v>
+        <v>-0.107</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5632</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3512</v>
+        <v>-0.1723</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.3512</v>
+        <v>-0.1723</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.3512</v>
+        <v>-0.1723</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.3512</v>
+        <v>-0.1723</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.3512</v>
+        <v>-0.1723</v>
       </c>
       <c r="N57" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.3865</v>
+        <v>-0.2381</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2399</v>
+        <v>-0.1478</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5775</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3865</v>
+        <v>-0.2381</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.3865</v>
+        <v>-0.2381</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.3865</v>
+        <v>-0.2381</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3865</v>
+        <v>-0.2381</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.3865</v>
+        <v>-0.2381</v>
       </c>
       <c r="N58" t="n">
-        <v>103</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>buda</t>
+          <t>kRaSnaL</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.4695</v>
+        <v>-0.3512</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2914</v>
+        <v>-0.218</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.611</v>
+        <v>-0.5838</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.4695</v>
+        <v>-0.3512</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0039</v>
+        <v>-0.3512</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.4734</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0039</v>
+        <v>-0.3512</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0032</v>
+        <v>-0.3512</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.4734</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="L59" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.4702</v>
+        <v>-0.3512</v>
       </c>
       <c r="N59" t="n">
-        <v>194</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.5524</v>
+        <v>-0.3865</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3429</v>
+        <v>-0.2399</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6445</v>
+        <v>-0.5979</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5524</v>
+        <v>-0.3865</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5524</v>
+        <v>-0.3865</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.5524</v>
+        <v>-0.3865</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5524</v>
+        <v>-0.3865</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.5524</v>
+        <v>-0.3865</v>
       </c>
       <c r="N60" t="n">
-        <v>129</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5971</v>
+        <v>-0.5524</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3706</v>
+        <v>-0.3429</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6626</v>
+        <v>-0.664</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5971</v>
+        <v>-0.5524</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.3439</v>
+        <v>-0.5524</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.2532</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.3439</v>
+        <v>-0.5524</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3487</v>
+        <v>-0.5524</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.2532</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="L61" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.6019</v>
+        <v>-0.5524</v>
       </c>
       <c r="N61" t="n">
-        <v>176</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.6163</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3826</v>
+        <v>-0.3682</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6703</v>
+        <v>-0.6802</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.6163</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.6163</v>
+        <v>-0.34</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>-0.2532</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.6163</v>
+        <v>-0.34</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.6163</v>
+        <v>-0.3487</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>-0.2532</v>
       </c>
       <c r="K62" t="n">
-        <v>68</v>
+        <v>140</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.6163</v>
+        <v>-0.6019</v>
       </c>
       <c r="N62" t="n">
-        <v>68</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6163</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4014</v>
+        <v>-0.3826</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6826</v>
+        <v>-0.6894</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6163</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6163</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6163</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6163</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>152</v>
+        <v>68</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6163</v>
       </c>
       <c r="N63" t="n">
-        <v>152</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64">
@@ -3354,7 +3354,7 @@
         <v>-0.4567</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7186</v>
+        <v>-0.7371</v>
       </c>
       <c r="E64" t="n">
         <v>-0.7358</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8759</v>
+        <v>-0.8726</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.5437</v>
+        <v>-0.5417</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7752</v>
+        <v>-0.7916</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8759</v>
+        <v>-0.8726</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8759</v>
+        <v>-0.8726</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8759</v>
+        <v>-0.8726</v>
       </c>
       <c r="I65" t="n">
         <v>-0.88</v>
@@ -3446,7 +3446,7 @@
         <v>-0.5813</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7996</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="E66" t="n">
         <v>-0.9364</v>
@@ -3492,7 +3492,7 @@
         <v>-0.593</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8073</v>
+        <v>-0.8245</v>
       </c>
       <c r="E67" t="n">
         <v>-0.9553</v>
@@ -3538,7 +3538,7 @@
         <v>-0.6254</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8284</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="E68" t="n">
         <v>-1.0075</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1559</v>
+        <v>-1.1473</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.7175</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8883</v>
+        <v>-0.901</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.1559</v>
+        <v>-1.1473</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.1559</v>
+        <v>-1.1473</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.1559</v>
+        <v>-1.1473</v>
       </c>
       <c r="I69" t="n">
         <v>-1.1667</v>
@@ -3630,7 +3630,7 @@
         <v>-0.7659</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9198</v>
+        <v>-0.9355</v>
       </c>
       <c r="E70" t="n">
         <v>-1.2339</v>
@@ -3676,7 +3676,7 @@
         <v>-0.8179999999999999</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9537</v>
+        <v>-0.9689</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3178</v>
@@ -3722,7 +3722,7 @@
         <v>-0.8662</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9851</v>
+        <v>-0.9999</v>
       </c>
       <c r="E72" t="n">
         <v>-1.3955</v>
@@ -3768,7 +3768,7 @@
         <v>-0.952</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0409</v>
+        <v>-1.0549</v>
       </c>
       <c r="E73" t="n">
         <v>-1.5336</v>
@@ -3814,7 +3814,7 @@
         <v>-0.9724</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0542</v>
+        <v>-1.068</v>
       </c>
       <c r="E74" t="n">
         <v>-1.5665</v>
@@ -3860,7 +3860,7 @@
         <v>-0.9805</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0595</v>
+        <v>-1.0732</v>
       </c>
       <c r="E75" t="n">
         <v>-1.5796</v>
@@ -3906,7 +3906,7 @@
         <v>-1.0783</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1232</v>
+        <v>-1.136</v>
       </c>
       <c r="E76" t="n">
         <v>-1.7372</v>
@@ -3952,7 +3952,7 @@
         <v>-1.1761</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1868</v>
+        <v>-1.1988</v>
       </c>
       <c r="E77" t="n">
         <v>-1.8947</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.0682</v>
+        <v>-2.0528</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.2838</v>
+        <v>-1.2743</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2569</v>
+        <v>-1.2617</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.0682</v>
+        <v>-2.0528</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.0682</v>
+        <v>-2.0528</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.0682</v>
+        <v>-2.0528</v>
       </c>
       <c r="I78" t="n">
         <v>-2.0875</v>
@@ -4044,7 +4044,7 @@
         <v>-2.1463</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.8182</v>
+        <v>-1.8214</v>
       </c>
       <c r="E79" t="n">
         <v>-3.4576</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.8082</v>
+        <v>-3.7921</v>
       </c>
       <c r="C80" t="n">
-        <v>-2.3639</v>
+        <v>-2.3539</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.9598</v>
+        <v>-1.9547</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.8082</v>
+        <v>-3.7921</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.1655</v>
+        <v>-2.1494</v>
       </c>
       <c r="G80" t="n">
         <v>-1.6427</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.1655</v>
+        <v>-2.1494</v>
       </c>
       <c r="I80" t="n">
         <v>-2.1857</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.9826</v>
+        <v>-4.9646</v>
       </c>
       <c r="C81" t="n">
-        <v>-3.0929</v>
+        <v>-3.0817</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.4342</v>
+        <v>-2.4218</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.9826</v>
+        <v>-4.9646</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.411</v>
+        <v>-2.393</v>
       </c>
       <c r="G81" t="n">
         <v>-2.5716</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.411</v>
+        <v>-2.393</v>
       </c>
       <c r="I81" t="n">
         <v>-2.4335</v>

--- a/database/event/7438/event_7438_evp_summary.xlsx
+++ b/database/event/7438/event_7438_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.2919</v>
+        <v>9.727399999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>5.7678</v>
+        <v>6.0382</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6057</v>
+        <v>3.7312</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2919</v>
+        <v>9.727399999999999</v>
       </c>
       <c r="F2" t="n">
         <v>3.1012</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.9573</v>
+        <v>9.1084</v>
       </c>
       <c r="C3" t="n">
-        <v>5.5601</v>
+        <v>5.6539</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4533</v>
+        <v>3.4547</v>
       </c>
       <c r="E3" t="n">
-        <v>8.9573</v>
+        <v>9.1084</v>
       </c>
       <c r="F3" t="n">
         <v>2.8757</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2325</v>
+        <v>6.4205</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8688</v>
+        <v>3.9855</v>
       </c>
       <c r="D4" t="n">
-        <v>2.213</v>
+        <v>2.2541</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2325</v>
+        <v>6.4205</v>
       </c>
       <c r="F4" t="n">
         <v>2.5684</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6356</v>
+        <v>4.697</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8775</v>
+        <v>2.9156</v>
       </c>
       <c r="D5" t="n">
-        <v>1.486</v>
+        <v>1.4842</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6356</v>
+        <v>4.697</v>
       </c>
       <c r="F5" t="n">
         <v>2.6377</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5467</v>
+        <v>4.5462</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8223</v>
+        <v>2.822</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4455</v>
+        <v>1.4169</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5467</v>
+        <v>4.5462</v>
       </c>
       <c r="F6" t="n">
         <v>0.7389</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0103</v>
+        <v>4.2671</v>
       </c>
       <c r="C7" t="n">
-        <v>2.4893</v>
+        <v>2.6488</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2014</v>
+        <v>1.2922</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0103</v>
+        <v>4.2671</v>
       </c>
       <c r="F7" t="n">
         <v>3.2707</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9503</v>
+        <v>3.9781</v>
       </c>
       <c r="C8" t="n">
-        <v>2.4521</v>
+        <v>2.4694</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1741</v>
+        <v>1.1631</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9503</v>
+        <v>3.9781</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1437</v>
+        <v>3.8353</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8066</v>
+        <v>0.0469</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1437</v>
+        <v>7.7597</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1512</v>
+        <v>4.1902</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8066</v>
+        <v>0.0469</v>
       </c>
       <c r="K8" t="n">
-        <v>191</v>
+        <v>99</v>
       </c>
       <c r="L8" t="n">
-        <v>166</v>
+        <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9578</v>
+        <v>4.2371</v>
       </c>
       <c r="N8" t="n">
-        <v>357</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8822</v>
+        <v>3.9533</v>
       </c>
       <c r="C9" t="n">
-        <v>2.4098</v>
+        <v>2.454</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1431</v>
+        <v>1.152</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8822</v>
+        <v>3.9533</v>
       </c>
       <c r="F9" t="n">
-        <v>3.8353</v>
+        <v>3.3984</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0469</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>7.7597</v>
+        <v>4.713</v>
       </c>
       <c r="I9" t="n">
-        <v>4.1902</v>
+        <v>4.713</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0469</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2371</v>
+        <v>4.713</v>
       </c>
       <c r="N9" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7697</v>
+        <v>3.9448</v>
       </c>
       <c r="C10" t="n">
-        <v>2.34</v>
+        <v>2.4487</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0918</v>
+        <v>1.1482</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7697</v>
+        <v>3.9448</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2977</v>
+        <v>0.1437</v>
       </c>
       <c r="G10" t="n">
-        <v>2.472</v>
+        <v>3.8066</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2977</v>
+        <v>0.1437</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2977</v>
+        <v>0.1512</v>
       </c>
       <c r="J10" t="n">
-        <v>2.472</v>
+        <v>3.8066</v>
       </c>
       <c r="K10" t="n">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="L10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7697</v>
+        <v>3.9578</v>
       </c>
       <c r="N10" t="n">
-        <v>281</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6054</v>
+        <v>3.7652</v>
       </c>
       <c r="C11" t="n">
-        <v>2.238</v>
+        <v>2.3372</v>
       </c>
       <c r="D11" t="n">
-        <v>1.017</v>
+        <v>1.068</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6054</v>
+        <v>3.7652</v>
       </c>
       <c r="F11" t="n">
         <v>3.5255</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.3984</v>
+        <v>3.746</v>
       </c>
       <c r="C12" t="n">
-        <v>2.1095</v>
+        <v>2.3253</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9228</v>
+        <v>1.0594</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3984</v>
+        <v>3.746</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3984</v>
+        <v>1.2977</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2.472</v>
       </c>
       <c r="H12" t="n">
-        <v>4.713</v>
+        <v>1.2977</v>
       </c>
       <c r="I12" t="n">
-        <v>4.713</v>
+        <v>1.2977</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2.472</v>
       </c>
       <c r="K12" t="n">
-        <v>162</v>
+        <v>117</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="M12" t="n">
-        <v>4.713</v>
+        <v>3.7697</v>
       </c>
       <c r="N12" t="n">
-        <v>162</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13">
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.3599</v>
+        <v>3.5865</v>
       </c>
       <c r="C13" t="n">
-        <v>2.0856</v>
+        <v>2.2263</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9053</v>
+        <v>0.9882</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3599</v>
+        <v>3.5865</v>
       </c>
       <c r="F13" t="n">
         <v>3.3599</v>
@@ -1044,81 +1044,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MartinezSa</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2186</v>
+        <v>3.3937</v>
       </c>
       <c r="C14" t="n">
-        <v>1.9979</v>
+        <v>2.1066</v>
       </c>
       <c r="D14" t="n">
-        <v>0.841</v>
+        <v>0.9021</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2186</v>
+        <v>3.3937</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1357</v>
+        <v>3.0248</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0829</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4516</v>
+        <v>3.8954</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9438</v>
+        <v>3.8954</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0829</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="L14" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0267</v>
+        <v>3.8954</v>
       </c>
       <c r="N14" t="n">
-        <v>194</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>MartinezSa</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.0697</v>
+        <v>3.3369</v>
       </c>
       <c r="C15" t="n">
-        <v>1.9055</v>
+        <v>2.0713</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7732</v>
+        <v>0.8767</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0697</v>
+        <v>3.3369</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5006</v>
+        <v>3.1357</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.0829</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3563</v>
+        <v>5.4516</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8124</v>
+        <v>2.9438</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.0829</v>
       </c>
       <c r="K15" t="n">
         <v>149</v>
@@ -1127,7 +1127,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3815</v>
+        <v>3.0267</v>
       </c>
       <c r="N15" t="n">
         <v>194</v>
@@ -1136,277 +1136,277 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.0676</v>
+        <v>3.2132</v>
       </c>
       <c r="C16" t="n">
-        <v>1.9042</v>
+        <v>1.9946</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7722</v>
+        <v>0.8214</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0676</v>
+        <v>3.2132</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0676</v>
+        <v>2.5006</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9891</v>
+        <v>3.3563</v>
       </c>
       <c r="I16" t="n">
-        <v>4.0919</v>
+        <v>1.8124</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M16" t="n">
-        <v>4.0919</v>
+        <v>2.3815</v>
       </c>
       <c r="N16" t="n">
-        <v>167</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.0248</v>
+        <v>3.1724</v>
       </c>
       <c r="C17" t="n">
-        <v>1.8776</v>
+        <v>1.9692</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7527</v>
+        <v>0.8032</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0248</v>
+        <v>3.1724</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0248</v>
+        <v>3.0676</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8954</v>
+        <v>3.9891</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8954</v>
+        <v>4.0919</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8954</v>
+        <v>4.0919</v>
       </c>
       <c r="N17" t="n">
-        <v>129</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.8016</v>
+        <v>3.0704</v>
       </c>
       <c r="C18" t="n">
-        <v>1.7391</v>
+        <v>1.9059</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6511</v>
+        <v>0.7577</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8016</v>
+        <v>3.0704</v>
       </c>
       <c r="F18" t="n">
-        <v>3.4802</v>
+        <v>2.7361</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6786</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4.8921</v>
+        <v>3.2635</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2801</v>
+        <v>3.2635</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6786</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="L18" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6015</v>
+        <v>3.2635</v>
       </c>
       <c r="N18" t="n">
-        <v>176</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.7361</v>
+        <v>3.036</v>
       </c>
       <c r="C19" t="n">
-        <v>1.6984</v>
+        <v>1.8846</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6213</v>
+        <v>0.7423</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7361</v>
+        <v>3.036</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7361</v>
+        <v>3.4802</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.6786</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2635</v>
+        <v>4.8921</v>
       </c>
       <c r="I19" t="n">
-        <v>3.2635</v>
+        <v>5.2801</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.6786</v>
       </c>
       <c r="K19" t="n">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2635</v>
+        <v>4.6015</v>
       </c>
       <c r="N19" t="n">
-        <v>152</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.547</v>
+        <v>2.6447</v>
       </c>
       <c r="C20" t="n">
-        <v>1.581</v>
+        <v>1.6417</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5352</v>
+        <v>0.5675</v>
       </c>
       <c r="E20" t="n">
-        <v>2.547</v>
+        <v>2.6447</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5384</v>
+        <v>2.4861</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0086</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.481</v>
+        <v>2.7163</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8797</v>
+        <v>2.8581</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0086</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>99</v>
+        <v>229</v>
       </c>
       <c r="L20" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8883</v>
+        <v>2.8581</v>
       </c>
       <c r="N20" t="n">
-        <v>142</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.5097</v>
+        <v>2.562</v>
       </c>
       <c r="C21" t="n">
-        <v>1.5579</v>
+        <v>1.5903</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5183</v>
+        <v>0.5306</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5097</v>
+        <v>2.562</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5097</v>
+        <v>2.5384</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.0086</v>
       </c>
       <c r="H21" t="n">
-        <v>2.768</v>
+        <v>3.481</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8393</v>
+        <v>1.8797</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.0086</v>
       </c>
       <c r="K21" t="n">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8393</v>
+        <v>1.8883</v>
       </c>
       <c r="N21" t="n">
-        <v>167</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22">
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.5017</v>
+        <v>2.534</v>
       </c>
       <c r="C22" t="n">
-        <v>1.5529</v>
+        <v>1.573</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5181</v>
       </c>
       <c r="E22" t="n">
-        <v>2.5017</v>
+        <v>2.534</v>
       </c>
       <c r="F22" t="n">
         <v>2.1786</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.4861</v>
+        <v>2.4984</v>
       </c>
       <c r="C23" t="n">
-        <v>1.5432</v>
+        <v>1.5509</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5075</v>
+        <v>0.5022</v>
       </c>
       <c r="E23" t="n">
-        <v>2.4861</v>
+        <v>2.4984</v>
       </c>
       <c r="F23" t="n">
-        <v>2.4861</v>
+        <v>2.5097</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.7163</v>
+        <v>2.768</v>
       </c>
       <c r="I23" t="n">
-        <v>2.8581</v>
+        <v>2.8393</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>229</v>
+        <v>167</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8581</v>
+        <v>2.8393</v>
       </c>
       <c r="N23" t="n">
-        <v>229</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.3649</v>
+        <v>2.3809</v>
       </c>
       <c r="C24" t="n">
-        <v>1.468</v>
+        <v>1.4779</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4523</v>
+        <v>0.4497</v>
       </c>
       <c r="E24" t="n">
-        <v>2.3649</v>
+        <v>2.3809</v>
       </c>
       <c r="F24" t="n">
         <v>2.3649</v>
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.2379</v>
+        <v>2.2362</v>
       </c>
       <c r="C25" t="n">
-        <v>1.3892</v>
+        <v>1.3881</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3945</v>
+        <v>0.385</v>
       </c>
       <c r="E25" t="n">
-        <v>2.2379</v>
+        <v>2.2362</v>
       </c>
       <c r="F25" t="n">
         <v>2.2379</v>
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.1964</v>
+        <v>2.2362</v>
       </c>
       <c r="C26" t="n">
-        <v>1.3634</v>
+        <v>1.3881</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3756</v>
+        <v>0.385</v>
       </c>
       <c r="E26" t="n">
-        <v>2.1964</v>
+        <v>2.2362</v>
       </c>
       <c r="F26" t="n">
         <v>2.1964</v>
@@ -1642,35 +1642,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.9721</v>
+        <v>2.011</v>
       </c>
       <c r="C27" t="n">
-        <v>1.2242</v>
+        <v>1.2483</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2735</v>
+        <v>0.2844</v>
       </c>
       <c r="E27" t="n">
-        <v>1.9721</v>
+        <v>2.011</v>
       </c>
       <c r="F27" t="n">
-        <v>2.7646</v>
+        <v>2.9101</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.7925</v>
+        <v>-0.9447</v>
       </c>
       <c r="H27" t="n">
-        <v>3.3259</v>
+        <v>3.6444</v>
       </c>
       <c r="I27" t="n">
-        <v>3.5897</v>
+        <v>3.9335</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.7925</v>
+        <v>-0.9447</v>
       </c>
       <c r="K27" t="n">
         <v>140</v>
@@ -1679,7 +1679,7 @@
         <v>36</v>
       </c>
       <c r="M27" t="n">
-        <v>2.7972</v>
+        <v>2.9888</v>
       </c>
       <c r="N27" t="n">
         <v>176</v>
@@ -1688,35 +1688,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.9654</v>
+        <v>1.9512</v>
       </c>
       <c r="C28" t="n">
-        <v>1.22</v>
+        <v>1.2112</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2705</v>
+        <v>0.2577</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9654</v>
+        <v>1.9512</v>
       </c>
       <c r="F28" t="n">
-        <v>2.9101</v>
+        <v>1.3497</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.9447</v>
+        <v>0.613</v>
       </c>
       <c r="H28" t="n">
-        <v>3.6444</v>
+        <v>1.3497</v>
       </c>
       <c r="I28" t="n">
-        <v>3.9335</v>
+        <v>1.4567</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9447</v>
+        <v>0.613</v>
       </c>
       <c r="K28" t="n">
         <v>140</v>
@@ -1725,7 +1725,7 @@
         <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>2.9888</v>
+        <v>2.0697</v>
       </c>
       <c r="N28" t="n">
         <v>176</v>
@@ -1734,231 +1734,231 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9627</v>
+        <v>1.9226</v>
       </c>
       <c r="C29" t="n">
-        <v>1.2183</v>
+        <v>1.1934</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2693</v>
+        <v>0.245</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9627</v>
+        <v>1.9226</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3497</v>
+        <v>2.3368</v>
       </c>
       <c r="G29" t="n">
-        <v>0.613</v>
+        <v>-0.4928</v>
       </c>
       <c r="H29" t="n">
-        <v>1.3497</v>
+        <v>2.3896</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4567</v>
+        <v>2.3896</v>
       </c>
       <c r="J29" t="n">
-        <v>0.613</v>
+        <v>-0.4928</v>
       </c>
       <c r="K29" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L29" t="n">
         <v>36</v>
       </c>
       <c r="M29" t="n">
-        <v>2.0697</v>
+        <v>1.8968</v>
       </c>
       <c r="N29" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.8899</v>
+        <v>1.797</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1731</v>
+        <v>1.1155</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2361</v>
+        <v>0.1889</v>
       </c>
       <c r="E30" t="n">
-        <v>1.8899</v>
+        <v>1.797</v>
       </c>
       <c r="F30" t="n">
-        <v>1.8899</v>
+        <v>1.6114</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.8899</v>
+        <v>1.6114</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8899</v>
+        <v>1.6114</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>162</v>
+        <v>63</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.8899</v>
+        <v>1.6114</v>
       </c>
       <c r="N30" t="n">
-        <v>162</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.8485</v>
+        <v>1.7923</v>
       </c>
       <c r="C31" t="n">
-        <v>1.1474</v>
+        <v>1.1125</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2173</v>
+        <v>0.1868</v>
       </c>
       <c r="E31" t="n">
-        <v>1.8485</v>
+        <v>1.7923</v>
       </c>
       <c r="F31" t="n">
-        <v>2.4142</v>
+        <v>2.7646</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5657</v>
+        <v>-0.7925</v>
       </c>
       <c r="H31" t="n">
-        <v>3.0712</v>
+        <v>3.3259</v>
       </c>
       <c r="I31" t="n">
-        <v>1.6584</v>
+        <v>3.5897</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5657</v>
+        <v>-0.7925</v>
       </c>
       <c r="K31" t="n">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="L31" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="M31" t="n">
-        <v>1.0927</v>
+        <v>2.7972</v>
       </c>
       <c r="N31" t="n">
-        <v>142</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.844</v>
+        <v>1.7271</v>
       </c>
       <c r="C32" t="n">
-        <v>1.1446</v>
+        <v>1.0721</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2152</v>
+        <v>0.1576</v>
       </c>
       <c r="E32" t="n">
-        <v>1.844</v>
+        <v>1.7271</v>
       </c>
       <c r="F32" t="n">
-        <v>2.3368</v>
+        <v>2.4142</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.4928</v>
+        <v>-0.5657</v>
       </c>
       <c r="H32" t="n">
-        <v>2.3896</v>
+        <v>3.0712</v>
       </c>
       <c r="I32" t="n">
-        <v>2.3896</v>
+        <v>1.6584</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.4928</v>
+        <v>-0.5657</v>
       </c>
       <c r="K32" t="n">
+        <v>99</v>
+      </c>
+      <c r="L32" t="n">
+        <v>43</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.0927</v>
+      </c>
+      <c r="N32" t="n">
         <v>142</v>
-      </c>
-      <c r="L32" t="n">
-        <v>36</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.8968</v>
-      </c>
-      <c r="N32" t="n">
-        <v>178</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.6906</v>
+        <v>1.6852</v>
       </c>
       <c r="C33" t="n">
-        <v>1.0494</v>
+        <v>1.0461</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1454</v>
+        <v>0.1389</v>
       </c>
       <c r="E33" t="n">
-        <v>1.6906</v>
+        <v>1.6852</v>
       </c>
       <c r="F33" t="n">
-        <v>2.0578</v>
+        <v>1.8899</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.3672</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.0578</v>
+        <v>1.8899</v>
       </c>
       <c r="I33" t="n">
-        <v>2.0578</v>
+        <v>1.8899</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.3672</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="L33" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.6906</v>
+        <v>1.8899</v>
       </c>
       <c r="N33" t="n">
-        <v>178</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34">
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.6517</v>
+        <v>1.6761</v>
       </c>
       <c r="C34" t="n">
-        <v>1.0253</v>
+        <v>1.0404</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1277</v>
+        <v>0.1349</v>
       </c>
       <c r="E34" t="n">
-        <v>1.6517</v>
+        <v>1.6761</v>
       </c>
       <c r="F34" t="n">
         <v>1.6517</v>
@@ -2010,185 +2010,185 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.6114</v>
+        <v>1.6759</v>
       </c>
       <c r="C35" t="n">
-        <v>1.0003</v>
+        <v>1.0403</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1093</v>
+        <v>0.1348</v>
       </c>
       <c r="E35" t="n">
-        <v>1.6114</v>
+        <v>1.6759</v>
       </c>
       <c r="F35" t="n">
-        <v>1.6114</v>
+        <v>2.0578</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.3672</v>
       </c>
       <c r="H35" t="n">
-        <v>1.6114</v>
+        <v>2.0578</v>
       </c>
       <c r="I35" t="n">
-        <v>1.6114</v>
+        <v>2.0578</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.3672</v>
       </c>
       <c r="K35" t="n">
-        <v>63</v>
+        <v>142</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M35" t="n">
-        <v>1.6114</v>
+        <v>1.6906</v>
       </c>
       <c r="N35" t="n">
-        <v>63</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.544</v>
+        <v>1.5685</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9584</v>
+        <v>0.9736</v>
       </c>
       <c r="D36" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0868</v>
       </c>
       <c r="E36" t="n">
-        <v>1.544</v>
+        <v>1.5685</v>
       </c>
       <c r="F36" t="n">
-        <v>1.544</v>
+        <v>1.4071</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.544</v>
+        <v>1.4071</v>
       </c>
       <c r="I36" t="n">
-        <v>1.544</v>
+        <v>1.4071</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.544</v>
+        <v>1.4071</v>
       </c>
       <c r="N36" t="n">
-        <v>152</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.5228</v>
+        <v>1.5251</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9453</v>
+        <v>0.9467</v>
       </c>
       <c r="D37" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0674</v>
       </c>
       <c r="E37" t="n">
-        <v>1.5228</v>
+        <v>1.5251</v>
       </c>
       <c r="F37" t="n">
-        <v>2.4129</v>
+        <v>1.544</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.8901</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3.0667</v>
+        <v>1.544</v>
       </c>
       <c r="I37" t="n">
-        <v>1.656</v>
+        <v>1.544</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.8901</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L37" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7658999999999999</v>
+        <v>1.544</v>
       </c>
       <c r="N37" t="n">
-        <v>194</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.4071</v>
+        <v>1.4987</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8734</v>
+        <v>0.9303</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0163</v>
+        <v>0.0556</v>
       </c>
       <c r="E38" t="n">
-        <v>1.4071</v>
+        <v>1.4987</v>
       </c>
       <c r="F38" t="n">
-        <v>1.4071</v>
+        <v>2.4129</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.8901</v>
       </c>
       <c r="H38" t="n">
-        <v>1.4071</v>
+        <v>3.0667</v>
       </c>
       <c r="I38" t="n">
-        <v>1.4071</v>
+        <v>1.656</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.8901</v>
       </c>
       <c r="K38" t="n">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M38" t="n">
-        <v>1.4071</v>
+        <v>0.7658999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>97</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39">
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.3271</v>
+        <v>1.3725</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8238</v>
+        <v>0.852</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0201</v>
+        <v>-0.0008</v>
       </c>
       <c r="E39" t="n">
-        <v>1.3271</v>
+        <v>1.3725</v>
       </c>
       <c r="F39" t="n">
         <v>1.3271</v>
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.2128</v>
+        <v>1.3239</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7528</v>
+        <v>0.8218</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0721</v>
+        <v>-0.0225</v>
       </c>
       <c r="E40" t="n">
-        <v>1.2128</v>
+        <v>1.3239</v>
       </c>
       <c r="F40" t="n">
         <v>1.6138</v>
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.2034</v>
+        <v>1.2915</v>
       </c>
       <c r="C41" t="n">
-        <v>0.747</v>
+        <v>0.8017</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0764</v>
+        <v>-0.0369</v>
       </c>
       <c r="E41" t="n">
-        <v>1.2034</v>
+        <v>1.2915</v>
       </c>
       <c r="F41" t="n">
         <v>1.2034</v>
@@ -2332,139 +2332,139 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>buda</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.1556</v>
+        <v>1.162</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7173</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0982</v>
+        <v>-0.0948</v>
       </c>
       <c r="E42" t="n">
-        <v>1.1556</v>
+        <v>1.162</v>
       </c>
       <c r="F42" t="n">
-        <v>1.4028</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.2472</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.4028</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7575</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.2472</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="L42" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5103</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>194</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>hAdji</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.979</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6142</v>
+        <v>0.6077</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1738</v>
+        <v>-0.1765</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.979</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.6645</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.6645</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.6645</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.6645</v>
       </c>
       <c r="N43" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>buda</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8714</v>
+        <v>0.9396</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5409</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2275</v>
+        <v>-0.1941</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8714</v>
+        <v>0.9396</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2315</v>
+        <v>1.4028</v>
       </c>
       <c r="G44" t="n">
-        <v>0.6399</v>
+        <v>-0.2472</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2315</v>
+        <v>1.4028</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2315</v>
+        <v>0.7575</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6399</v>
+        <v>-0.2472</v>
       </c>
       <c r="K44" t="n">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="L44" t="n">
-        <v>164</v>
+        <v>45</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8714000000000001</v>
+        <v>0.5103</v>
       </c>
       <c r="N44" t="n">
-        <v>281</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45">
@@ -2474,16 +2474,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7984</v>
+        <v>0.9075</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4956</v>
+        <v>0.5633</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2608</v>
+        <v>-0.2085</v>
       </c>
       <c r="E45" t="n">
-        <v>0.7984</v>
+        <v>0.9075</v>
       </c>
       <c r="F45" t="n">
         <v>0.7984</v>
@@ -2520,16 +2520,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6957</v>
+        <v>0.7602</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4318</v>
+        <v>0.4719</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3075</v>
+        <v>-0.2743</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6957</v>
+        <v>0.7602</v>
       </c>
       <c r="F46" t="n">
         <v>0.6957</v>
@@ -2562,139 +2562,139 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>hAdji</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6645</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4125</v>
+        <v>0.4527</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3217</v>
+        <v>-0.2881</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6645</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6645</v>
+        <v>0.437</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6645</v>
+        <v>0.437</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6645</v>
+        <v>0.437</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6645</v>
+        <v>0.437</v>
       </c>
       <c r="N47" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4435</v>
+        <v>0.6684</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2753</v>
+        <v>0.4149</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4223</v>
+        <v>-0.3153</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4435</v>
+        <v>0.6684</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4435</v>
+        <v>0.2315</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.6399</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4435</v>
+        <v>0.2315</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4435</v>
+        <v>0.2315</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>0.6399</v>
       </c>
       <c r="K48" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4435</v>
+        <v>0.8714000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>103</v>
+        <v>281</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.437</v>
+        <v>0.4503</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2713</v>
+        <v>0.2795</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4253</v>
+        <v>-0.4127</v>
       </c>
       <c r="E49" t="n">
-        <v>0.437</v>
+        <v>0.4503</v>
       </c>
       <c r="F49" t="n">
-        <v>0.437</v>
+        <v>0.1849</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.437</v>
+        <v>0.1849</v>
       </c>
       <c r="I49" t="n">
-        <v>0.437</v>
+        <v>0.1849</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.437</v>
+        <v>0.1849</v>
       </c>
       <c r="N49" t="n">
-        <v>103</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50">
@@ -2704,16 +2704,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.367</v>
+        <v>0.4247</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2278</v>
+        <v>0.2636</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4571</v>
+        <v>-0.4241</v>
       </c>
       <c r="E50" t="n">
-        <v>0.367</v>
+        <v>0.4247</v>
       </c>
       <c r="F50" t="n">
         <v>0.367</v>
@@ -2746,47 +2746,47 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.3158</v>
+        <v>0.3945</v>
       </c>
       <c r="C51" t="n">
-        <v>0.196</v>
+        <v>0.2449</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4804</v>
+        <v>-0.4376</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3158</v>
+        <v>0.3945</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3158</v>
+        <v>0.4435</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3158</v>
+        <v>0.4435</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3158</v>
+        <v>0.4435</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.3158</v>
+        <v>0.4435</v>
       </c>
       <c r="N51" t="n">
-        <v>152</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52">
@@ -2796,16 +2796,16 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.2828</v>
+        <v>0.2941</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1755</v>
+        <v>0.1826</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4955</v>
+        <v>-0.4825</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2828</v>
+        <v>0.2941</v>
       </c>
       <c r="F52" t="n">
         <v>0.2935</v>
@@ -2838,170 +2838,170 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.2474</v>
+        <v>0.2374</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1536</v>
+        <v>0.1474</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.5078</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2474</v>
+        <v>0.2374</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2474</v>
+        <v>0.3158</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2474</v>
+        <v>0.3158</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2474</v>
+        <v>0.3158</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.2474</v>
+        <v>0.3158</v>
       </c>
       <c r="N53" t="n">
-        <v>129</v>
+        <v>152</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>kRaSnaL</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2127</v>
+        <v>0.204</v>
       </c>
       <c r="C54" t="n">
-        <v>0.132</v>
+        <v>0.1266</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5274</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2127</v>
+        <v>0.204</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2127</v>
+        <v>-0.0416</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2127</v>
+        <v>-0.0416</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2127</v>
+        <v>-0.0416</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>152</v>
+        <v>68</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2127</v>
+        <v>-0.0416</v>
       </c>
       <c r="N54" t="n">
-        <v>152</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.1849</v>
+        <v>0.1573</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1148</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.54</v>
+        <v>-0.5436</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1849</v>
+        <v>0.1573</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1849</v>
+        <v>0.2127</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1849</v>
+        <v>0.2127</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1849</v>
+        <v>0.2127</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>62</v>
+        <v>152</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1849</v>
+        <v>0.2127</v>
       </c>
       <c r="N55" t="n">
-        <v>62</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.1748</v>
+        <v>0.1355</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1085</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5446</v>
+        <v>-0.5533</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1748</v>
+        <v>0.1355</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1748</v>
+        <v>0.143</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1748</v>
+        <v>0.143</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1748</v>
+        <v>0.143</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1748</v>
+        <v>0.143</v>
       </c>
       <c r="N56" t="n">
         <v>97</v>
@@ -3022,47 +3022,47 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.143</v>
+        <v>0.1189</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0888</v>
+        <v>0.0738</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5591</v>
+        <v>-0.5607</v>
       </c>
       <c r="E57" t="n">
-        <v>0.143</v>
+        <v>0.1189</v>
       </c>
       <c r="F57" t="n">
-        <v>0.143</v>
+        <v>0.2474</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.143</v>
+        <v>0.2474</v>
       </c>
       <c r="I57" t="n">
-        <v>0.143</v>
+        <v>0.2474</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.143</v>
+        <v>0.2474</v>
       </c>
       <c r="N57" t="n">
-        <v>97</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58">
@@ -3072,16 +3072,16 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.1415</v>
+        <v>0.0974</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0878</v>
+        <v>0.0605</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5598</v>
+        <v>-0.5703</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1415</v>
+        <v>0.0974</v>
       </c>
       <c r="F58" t="n">
         <v>0.4594</v>
@@ -3114,93 +3114,93 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.1336</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0829</v>
+        <v>-0.0055</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5634</v>
+        <v>-0.6178</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1336</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1336</v>
+        <v>0.1748</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1336</v>
+        <v>0.1748</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1336</v>
+        <v>0.1748</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1336</v>
+        <v>0.1748</v>
       </c>
       <c r="N59" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kRaSnaL</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.0416</v>
+        <v>-0.0417</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0258</v>
+        <v>-0.0259</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6431</v>
+        <v>-0.6324</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.0416</v>
+        <v>-0.0417</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.0416</v>
+        <v>-0.1733</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.0416</v>
+        <v>-0.1733</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0416</v>
+        <v>-0.1733</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.0416</v>
+        <v>-0.1733</v>
       </c>
       <c r="N60" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61">
@@ -3210,16 +3210,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.0421</v>
+        <v>-0.2012</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0261</v>
+        <v>-0.1249</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6434</v>
+        <v>-0.7037</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.0421</v>
+        <v>-0.2012</v>
       </c>
       <c r="F61" t="n">
         <v>-0.0421</v>
@@ -3252,93 +3252,93 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.0696</v>
+        <v>-0.2643</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0432</v>
+        <v>-0.1641</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6559</v>
+        <v>-0.7319</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.0696</v>
+        <v>-0.2643</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.0696</v>
+        <v>0.1336</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.0696</v>
+        <v>0.1336</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.0696</v>
+        <v>0.1336</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.0696</v>
+        <v>0.1336</v>
       </c>
       <c r="N62" t="n">
-        <v>129</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.1733</v>
+        <v>-0.4332</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1076</v>
+        <v>-0.2689</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7030999999999999</v>
+        <v>-0.8073</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.1733</v>
+        <v>-0.4332</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.1733</v>
+        <v>-0.0696</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.1733</v>
+        <v>-0.0696</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1733</v>
+        <v>-0.0696</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.1733</v>
+        <v>-0.0696</v>
       </c>
       <c r="N63" t="n">
-        <v>103</v>
+        <v>129</v>
       </c>
     </row>
     <row r="64">
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.4439</v>
+        <v>-0.543</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2755</v>
+        <v>-0.3371</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8263</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.4439</v>
+        <v>-0.543</v>
       </c>
       <c r="F64" t="n">
         <v>-0.4439</v>
@@ -3394,16 +3394,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.552</v>
+        <v>-0.6634</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3426</v>
+        <v>-0.4118</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.9101</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.552</v>
+        <v>-0.6634</v>
       </c>
       <c r="F65" t="n">
         <v>-0.552</v>
@@ -3436,323 +3436,323 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.5556</v>
+        <v>-0.7459</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3449</v>
+        <v>-0.463</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8771</v>
+        <v>-0.947</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.5556</v>
+        <v>-0.7459</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.5556</v>
+        <v>-0.5802</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.5556</v>
+        <v>-0.5802</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5556</v>
+        <v>-0.5802</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>62</v>
+        <v>152</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.5556</v>
+        <v>-0.5802</v>
       </c>
       <c r="N66" t="n">
-        <v>62</v>
+        <v>152</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>Woro2k</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5802</v>
+        <v>-0.7653</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3602</v>
+        <v>-0.4751</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8883</v>
+        <v>-0.9557</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5802</v>
+        <v>-0.7653</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5802</v>
+        <v>-0.7029</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5802</v>
+        <v>-0.7029</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.5802</v>
+        <v>-0.7029</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>152</v>
+        <v>68</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.5802</v>
+        <v>-0.7029</v>
       </c>
       <c r="N67" t="n">
-        <v>152</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Woro2k</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.7029</v>
+        <v>-0.8337</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4363</v>
+        <v>-0.5175</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9442</v>
+        <v>-0.9862</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.7029</v>
+        <v>-0.8337</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.7029</v>
+        <v>-0.5556</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.7029</v>
+        <v>-0.5556</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.7029</v>
+        <v>-0.5556</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.7029</v>
+        <v>-0.5556</v>
       </c>
       <c r="N68" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.9358</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4502</v>
+        <v>-0.5809</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9544</v>
+        <v>-1.0318</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.9358</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.8712</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.8712</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.8712</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.8712</v>
       </c>
       <c r="N69" t="n">
-        <v>63</v>
+        <v>97</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.7321</v>
+        <v>-0.9568</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4544</v>
+        <v>-0.5939</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9575</v>
+        <v>-1.0412</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.7321</v>
+        <v>-0.9568</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.7321</v>
+        <v>-0.9194</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.7321</v>
+        <v>-0.9194</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7321</v>
+        <v>-0.9194</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>162</v>
+        <v>63</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.7321</v>
+        <v>-0.9194</v>
       </c>
       <c r="N70" t="n">
-        <v>162</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.8712</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.6123</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0208</v>
+        <v>-1.0544</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.8712</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.8712</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.8712</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8712</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.8712</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="N71" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9194</v>
+        <v>-1.07</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5707</v>
+        <v>-0.6642</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0427</v>
+        <v>-1.0918</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9194</v>
+        <v>-1.07</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.9194</v>
+        <v>-0.7321</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.9194</v>
+        <v>-0.7321</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.9194</v>
+        <v>-0.7321</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>63</v>
+        <v>162</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9194</v>
+        <v>-0.7321</v>
       </c>
       <c r="N72" t="n">
-        <v>63</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73">
@@ -3762,16 +3762,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.9405</v>
+        <v>-1.1404</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5838</v>
+        <v>-0.7079</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0523</v>
+        <v>-1.1232</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.9405</v>
+        <v>-1.1404</v>
       </c>
       <c r="F73" t="n">
         <v>-0.9405</v>
@@ -3804,139 +3804,139 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.1146</v>
+        <v>-1.2097</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6919</v>
+        <v>-0.7509</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1316</v>
+        <v>-1.1542</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1146</v>
+        <v>-1.2097</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.1146</v>
+        <v>-1.1434</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.1146</v>
+        <v>-1.1434</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.1146</v>
+        <v>-1.1434</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.1146</v>
+        <v>-1.1434</v>
       </c>
       <c r="N74" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.1434</v>
+        <v>-1.312</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7098</v>
+        <v>-0.8144</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1447</v>
+        <v>-1.1999</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.1434</v>
+        <v>-1.312</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.1434</v>
+        <v>-1.1835</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.1434</v>
+        <v>-1.1835</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.1434</v>
+        <v>-1.2453</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>63</v>
+        <v>229</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.1434</v>
+        <v>-1.2453</v>
       </c>
       <c r="N75" t="n">
-        <v>63</v>
+        <v>229</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.1835</v>
+        <v>-1.4255</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7346</v>
+        <v>-0.8849</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.163</v>
+        <v>-1.2506</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.1835</v>
+        <v>-1.4255</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.1835</v>
+        <v>-1.1146</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.1835</v>
+        <v>-1.1146</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2453</v>
+        <v>-1.1146</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>229</v>
+        <v>62</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.2453</v>
+        <v>-1.1146</v>
       </c>
       <c r="N76" t="n">
-        <v>229</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77">
@@ -3946,16 +3946,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.2068</v>
+        <v>-1.4796</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7491</v>
+        <v>-0.9184</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1736</v>
+        <v>-1.2747</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.2068</v>
+        <v>-1.4796</v>
       </c>
       <c r="F77" t="n">
         <v>-1.2068</v>
@@ -3992,16 +3992,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.3993</v>
+        <v>-1.805</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.8686</v>
+        <v>-1.1204</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2612</v>
+        <v>-1.4201</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.3993</v>
+        <v>-1.805</v>
       </c>
       <c r="F78" t="n">
         <v>-1.3993</v>
@@ -4034,93 +4034,93 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.5205</v>
+        <v>-2.7408</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.5646</v>
+        <v>-1.7013</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.7716</v>
+        <v>-1.8381</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.5205</v>
+        <v>-2.7408</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.3119</v>
+        <v>-2.0086</v>
       </c>
       <c r="G79" t="n">
-        <v>-1.2086</v>
+        <v>-0.5383</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.3119</v>
+        <v>-2.0086</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.3804</v>
+        <v>-2.0086</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.2086</v>
+        <v>-0.5383</v>
       </c>
       <c r="K79" t="n">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="L79" t="n">
-        <v>166</v>
+        <v>36</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.589</v>
+        <v>-2.5469</v>
       </c>
       <c r="N79" t="n">
-        <v>357</v>
+        <v>178</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.5469</v>
+        <v>-2.862</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.581</v>
+        <v>-1.7766</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.7836</v>
+        <v>-1.8922</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.5469</v>
+        <v>-2.862</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.0086</v>
+        <v>-1.3119</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.5383</v>
+        <v>-1.2086</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.0086</v>
+        <v>-1.3119</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.0086</v>
+        <v>-1.3804</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.5383</v>
+        <v>-1.2086</v>
       </c>
       <c r="K80" t="n">
-        <v>142</v>
+        <v>191</v>
       </c>
       <c r="L80" t="n">
-        <v>36</v>
+        <v>166</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.5469</v>
+        <v>-2.589</v>
       </c>
       <c r="N80" t="n">
-        <v>178</v>
+        <v>357</v>
       </c>
     </row>
     <row r="81">
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.1032</v>
+        <v>-4.3632</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.547</v>
+        <v>-2.7084</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.4921</v>
+        <v>-2.5628</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.1032</v>
+        <v>-4.3632</v>
       </c>
       <c r="F81" t="n">
         <v>-1.8933</v>
